--- a/Copper/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Copper/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Sensitivity analyses/Plots of HA SA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/7. Sensitivity analyses/Plots of HA SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_A79D70068FBA1553F057F5993CC2F1A8C6DAC88D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD8F4E4F-C10B-44EC-8FBB-DA57DD9F0DCD}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_A79D70068FFA7D6F5ACA2FF92020F1A8C6DAC8F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C3E7E0-EEF1-456A-AA87-FA5789491BB8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HA_Sensitivity_Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Overall_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HA_Sensitivity_Summary!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -81,6 +84,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -110,8 +118,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -127,6 +140,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,9 +428,13 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -453,22 +474,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>-1.09260281521799E-8</v>
+        <v>-1.19059117242522E-8</v>
       </c>
       <c r="D2">
-        <v>2.17270477644284E-9</v>
-      </c>
-      <c r="E2">
-        <v>-24.059547975557098</v>
-      </c>
-      <c r="F2">
-        <v>0.519364390345745</v>
-      </c>
-      <c r="G2">
-        <v>-0.12073939500174199</v>
-      </c>
-      <c r="H2">
-        <v>2.8542463434671401E-3</v>
+        <v>2.2598270727554102E-9</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-24.481767587299501</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.53521079830227403</v>
+      </c>
+      <c r="G2" s="5">
+        <v>-0.12324963046968</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.9567469100795899E-3</v>
       </c>
       <c r="I2">
         <v>127</v>
@@ -482,22 +503,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>-6.3678932877189597E-9</v>
+        <v>-6.93655114392823E-9</v>
       </c>
       <c r="D3">
-        <v>1.2203226178216799E-9</v>
-      </c>
-      <c r="E3">
-        <v>-19.375460560959901</v>
-      </c>
-      <c r="F3">
-        <v>0.37381970195942799</v>
-      </c>
-      <c r="G3">
-        <v>-9.4096019952525298E-2</v>
-      </c>
-      <c r="H3">
-        <v>1.94997087929842E-3</v>
+        <v>1.27972129276601E-9</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-19.653275411831402</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.38250546673376501</v>
+      </c>
+      <c r="G3" s="5">
+        <v>-9.5624737054488596E-2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.9998607951736301E-3</v>
       </c>
       <c r="I3">
         <v>127</v>
@@ -511,22 +532,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>-4.1088110003622802E-9</v>
+        <v>-4.4720823946970601E-9</v>
       </c>
       <c r="D4">
-        <v>7.5131180716449203E-10</v>
-      </c>
-      <c r="E4">
-        <v>-16.197803822626302</v>
-      </c>
-      <c r="F4">
-        <v>0.28319870749264198</v>
-      </c>
-      <c r="G4">
-        <v>-7.7046097961504106E-2</v>
-      </c>
-      <c r="H4">
-        <v>1.4291458497539601E-3</v>
+        <v>7.9282317180501699E-10</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-16.394265508947999</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.28880151375319202</v>
+      </c>
+      <c r="G4" s="5">
+        <v>-7.8078522723066604E-2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1.4593381844048799E-3</v>
       </c>
       <c r="I4">
         <v>127</v>
@@ -540,22 +561,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>-2.8563219839907499E-9</v>
+        <v>-3.1052782575033E-9</v>
       </c>
       <c r="D5">
-        <v>5.0014566304099601E-10</v>
-      </c>
-      <c r="E5">
-        <v>-13.9104938183375</v>
-      </c>
-      <c r="F5">
-        <v>0.22267357310752001</v>
-      </c>
-      <c r="G5">
-        <v>-6.52273730983602E-2</v>
-      </c>
-      <c r="H5">
-        <v>1.09825262901874E-3</v>
+        <v>5.3017494796820905E-10</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-14.0566600272471</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.226644723961649</v>
+      </c>
+      <c r="G5" s="5">
+        <v>-6.5972180043505496E-2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.11883018249847E-3</v>
       </c>
       <c r="I5">
         <v>127</v>
@@ -569,22 +590,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>-2.0977583128581201E-9</v>
+        <v>-2.2776386031790999E-9</v>
       </c>
       <c r="D6">
-        <v>3.5387651237156097E-10</v>
-      </c>
-      <c r="E6">
-        <v>-12.1886399909429</v>
-      </c>
-      <c r="F6">
-        <v>0.180179325270342</v>
-      </c>
-      <c r="G6">
-        <v>-5.65615224331752E-2</v>
-      </c>
-      <c r="H6">
-        <v>8.7391977310204204E-4</v>
+        <v>3.7631175504971798E-10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-12.3015203532517</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.18315939980589199</v>
+      </c>
+      <c r="G6" s="5">
+        <v>-5.7124105483203798E-2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8.8895499149945097E-4</v>
       </c>
       <c r="I6">
         <v>127</v>
@@ -603,16 +624,16 @@
       <c r="D7">
         <v>7.3251067439953397E-10</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>-39.244354607895197</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>0.908466087854785</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>-0.217024126734495</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>6.3369359833470697E-3</v>
       </c>
       <c r="I7">
@@ -632,16 +653,16 @@
       <c r="D8">
         <v>2.98774498861813E-10</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>-28.186250399990399</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>0.48188133704483499</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="5">
         <v>-0.143917388131278</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>2.8778657703789502E-3</v>
       </c>
       <c r="I8">
@@ -661,16 +682,16 @@
       <c r="D9">
         <v>1.62168698509139E-10</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>-21.9860667878466</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>0.29777385282191998</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="5">
         <v>-0.107868538314292</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>1.6451486030233599E-3</v>
       </c>
       <c r="I9">
@@ -690,16 +711,16 @@
       <c r="D10">
         <v>1.01814451582528E-10</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>-18.021615134053501</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>0.20207024340398799</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="5">
         <v>-8.6317678369347103E-2</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>1.0650924981916599E-3</v>
       </c>
       <c r="I10">
@@ -719,16 +740,16 @@
       <c r="D11">
         <v>6.9870687123835403E-11</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>-15.269390504529101</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>0.14616193240070599</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="5">
         <v>-7.1968029178878901E-2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>7.4645770395046103E-4</v>
       </c>
       <c r="I11">
@@ -743,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1.01365266565971E-8</v>
+        <v>-9.2865839471915692E-9</v>
       </c>
       <c r="D12">
-        <v>2.6141429012697801E-9</v>
-      </c>
-      <c r="E12">
-        <v>-31.412756741329499</v>
-      </c>
-      <c r="F12">
-        <v>0.47877752008804703</v>
-      </c>
-      <c r="G12">
-        <v>-0.16477251951966401</v>
-      </c>
-      <c r="H12">
-        <v>3.0087729950325102E-3</v>
+        <v>2.6031957059709699E-9</v>
+      </c>
+      <c r="E12" s="4">
+        <v>-31.253781249072802</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.52540825112168099</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-0.16389943093616</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3.2801020199202499E-3</v>
       </c>
       <c r="I12">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -772,25 +793,25 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>-5.2943173412861398E-9</v>
+        <v>-4.7673824826385602E-9</v>
       </c>
       <c r="D13">
-        <v>1.48290068883031E-9</v>
-      </c>
-      <c r="E13">
-        <v>-23.9286150564038</v>
-      </c>
-      <c r="F13">
-        <v>0.28569144846372302</v>
-      </c>
-      <c r="G13">
-        <v>-0.11907306301637199</v>
-      </c>
-      <c r="H13">
-        <v>1.61998195318168E-3</v>
+        <v>1.45833273144917E-9</v>
+      </c>
+      <c r="E13" s="4">
+        <v>-23.807263537815</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.317185090512003</v>
+      </c>
+      <c r="G13" s="5">
+        <v>-0.11842802169545601</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1.7899857445658901E-3</v>
       </c>
       <c r="I13">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -801,25 +822,25 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>-3.2151860050683001E-9</v>
+        <v>-2.8682166900706298E-9</v>
       </c>
       <c r="D14">
-        <v>9.2949787986574601E-10</v>
-      </c>
-      <c r="E14">
-        <v>-19.316529347585199</v>
-      </c>
-      <c r="F14">
-        <v>0.19071054944098301</v>
-      </c>
-      <c r="G14">
-        <v>-9.3332301387409E-2</v>
-      </c>
-      <c r="H14">
-        <v>1.02126338610707E-3</v>
+        <v>9.0694230920384996E-10</v>
+      </c>
+      <c r="E14" s="4">
+        <v>-19.223301833483699</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.21320947679048399</v>
+      </c>
+      <c r="G14" s="5">
+        <v>-9.2851680497376798E-2</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1.13767832353614E-3</v>
       </c>
       <c r="I14">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -830,25 +851,25 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>-2.1417045945004599E-9</v>
+        <v>-1.8997164885501501E-9</v>
       </c>
       <c r="D15">
-        <v>6.2417403788780096E-10</v>
-      </c>
-      <c r="E15">
-        <v>-16.1925691927188</v>
-      </c>
-      <c r="F15">
-        <v>0.136803551247869</v>
-      </c>
-      <c r="G15">
-        <v>-7.6773316236436906E-2</v>
-      </c>
-      <c r="H15">
-        <v>7.0626124176752898E-4</v>
+        <v>6.0512015261538299E-10</v>
+      </c>
+      <c r="E15" s="4">
+        <v>-16.119476250399099</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.15359840867670699</v>
+      </c>
+      <c r="G15" s="5">
+        <v>-7.6405346897304105E-2</v>
+      </c>
+      <c r="H15" s="5">
+        <v>7.9076163339964302E-4</v>
       </c>
       <c r="I15">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -859,25 +880,25 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>-1.52126988823109E-9</v>
+        <v>-1.34443626084822E-9</v>
       </c>
       <c r="D16">
-        <v>4.42614365083958E-10</v>
-      </c>
-      <c r="E16">
-        <v>-13.937346442031799</v>
-      </c>
-      <c r="F16">
-        <v>0.10309180072841601</v>
-      </c>
-      <c r="G16">
-        <v>-6.52153796755085E-2</v>
-      </c>
-      <c r="H16">
-        <v>5.1879308014864199E-4</v>
+        <v>4.2678410479106698E-10</v>
+      </c>
+      <c r="E16" s="4">
+        <v>-13.8788674552928</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.116078615071631</v>
+      </c>
+      <c r="G16" s="5">
+        <v>-6.4926351335349505E-2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5.8283652568377298E-4</v>
       </c>
       <c r="I16">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -888,25 +909,25 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-5.2069365075992201E-9</v>
+        <v>-5.0368333032264102E-9</v>
       </c>
       <c r="D17">
-        <v>4.1839707087580999E-10</v>
-      </c>
-      <c r="E17">
-        <v>-28.166566933406699</v>
-      </c>
-      <c r="F17">
-        <v>0.38153683863107801</v>
-      </c>
-      <c r="G17">
-        <v>-0.14437269864643701</v>
-      </c>
-      <c r="H17">
-        <v>2.2801514578666298E-3</v>
+        <v>4.0837018720014301E-10</v>
+      </c>
+      <c r="E17" s="4">
+        <v>-27.981270041014898</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.37585122914302899</v>
+      </c>
+      <c r="G17" s="5">
+        <v>-0.14326119404155099</v>
+      </c>
+      <c r="H17" s="5">
+        <v>2.2460670238699E-3</v>
       </c>
       <c r="I17">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -917,25 +938,25 @@
         <v>11</v>
       </c>
       <c r="C18">
-        <v>-2.8711078950595602E-9</v>
+        <v>-2.78013610282006E-9</v>
       </c>
       <c r="D18">
-        <v>2.3206884573858301E-10</v>
-      </c>
-      <c r="E18">
-        <v>-21.975638509488999</v>
-      </c>
-      <c r="F18">
-        <v>0.238732918197057</v>
-      </c>
-      <c r="G18">
-        <v>-0.108001931629995</v>
-      </c>
-      <c r="H18">
-        <v>1.31351800505018E-3</v>
+        <v>2.2627721355092101E-10</v>
+      </c>
+      <c r="E18" s="4">
+        <v>-21.8589834922976</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.235295450575286</v>
+      </c>
+      <c r="G18" s="5">
+        <v>-0.107356008907272</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1.29484582590559E-3</v>
       </c>
       <c r="I18">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -946,25 +967,25 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>-1.8202102705400799E-9</v>
+        <v>-1.7637148433835899E-9</v>
       </c>
       <c r="D19">
-        <v>1.4685233125198801E-10</v>
-      </c>
-      <c r="E19">
-        <v>-18.012033690238599</v>
-      </c>
-      <c r="F19">
-        <v>0.16385362156413799</v>
-      </c>
-      <c r="G19">
-        <v>-8.6349189745943203E-2</v>
-      </c>
-      <c r="H19">
-        <v>8.59564182326996E-4</v>
+        <v>1.4312306896317999E-10</v>
+      </c>
+      <c r="E19" s="4">
+        <v>-17.932050107741201</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.16150826521786699</v>
+      </c>
+      <c r="G19" s="5">
+        <v>-8.5927020534974904E-2</v>
+      </c>
+      <c r="H19" s="5">
+        <v>8.4745030798387703E-4</v>
       </c>
       <c r="I19">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -975,25 +996,25 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>-1.2572913099713499E-9</v>
+        <v>-1.21884469964291E-9</v>
       </c>
       <c r="D20">
-        <v>1.00967193306608E-10</v>
-      </c>
-      <c r="E20">
-        <v>-15.2593635143343</v>
-      </c>
-      <c r="F20">
-        <v>0.119616550477939</v>
-      </c>
-      <c r="G20">
-        <v>-7.1957936590276994E-2</v>
-      </c>
-      <c r="H20">
-        <v>6.0818545475408998E-4</v>
+        <v>9.8383099073271503E-11</v>
+      </c>
+      <c r="E20" s="4">
+        <v>-15.201171411843699</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.117895897904221</v>
+      </c>
+      <c r="G20" s="5">
+        <v>-7.1660457612708894E-2</v>
+      </c>
+      <c r="H20" s="5">
+        <v>5.9956425597069204E-4</v>
       </c>
       <c r="I20">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1004,28 +1025,29 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>-9.2063680872680401E-10</v>
+        <v>-8.9279988965602096E-10</v>
       </c>
       <c r="D21">
-        <v>7.3552110367049995E-11</v>
-      </c>
-      <c r="E21">
-        <v>-13.2367059370623</v>
-      </c>
-      <c r="F21">
-        <v>9.1252804054104797E-2</v>
-      </c>
-      <c r="G21">
-        <v>-6.1691588645189303E-2</v>
-      </c>
-      <c r="H21">
-        <v>4.5379202529484397E-4</v>
+        <v>7.1662793608305305E-11</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-13.1924923491801</v>
+      </c>
+      <c r="F21" s="1">
+        <v>8.9928473912002094E-2</v>
+      </c>
+      <c r="G21" s="5">
+        <v>-6.14706914602118E-2</v>
+      </c>
+      <c r="H21" s="5">
+        <v>4.4729108721568302E-4</v>
       </c>
       <c r="I21">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1035,10 +1057,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1071,22 +1089,22 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>-5.2713625474220001E-9</v>
+        <v>-5.7394924247119703E-9</v>
       </c>
       <c r="C2">
-        <v>5.4780682327596795E-10</v>
-      </c>
-      <c r="D2">
-        <v>-17.146389233684701</v>
-      </c>
-      <c r="E2">
-        <v>0.22518736223754099</v>
-      </c>
-      <c r="F2">
-        <v>-8.2734081689461295E-2</v>
-      </c>
-      <c r="G2">
-        <v>1.20572797499709E-3</v>
+        <v>5.7339942860956104E-10</v>
+      </c>
+      <c r="D2" s="3">
+        <v>-17.377497777715501</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.230994605405206</v>
+      </c>
+      <c r="F2" s="5">
+        <v>-8.4009835154788798E-2</v>
+      </c>
+      <c r="G2" s="5">
+        <v>1.24190077293871E-3</v>
       </c>
       <c r="H2">
         <v>635</v>
@@ -1102,16 +1120,16 @@
       <c r="C3">
         <v>2.3238676551931099E-10</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>-24.541535486863001</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>1.0497457234916101</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>-0.12541915214565799</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="5">
         <v>6.3962192186656297E-3</v>
       </c>
       <c r="H3">
@@ -1123,25 +1141,25 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-4.46180089713661E-9</v>
+        <v>-4.03326717385982E-9</v>
       </c>
       <c r="C4">
-        <v>6.6006539245574302E-10</v>
-      </c>
-      <c r="D4">
-        <v>-20.9575633560138</v>
-      </c>
-      <c r="E4">
-        <v>0.306271366882927</v>
-      </c>
-      <c r="F4">
-        <v>-0.103833315967078</v>
-      </c>
-      <c r="G4">
-        <v>1.7616722643256E-3</v>
+        <v>6.5208678559708204E-10</v>
+      </c>
+      <c r="D4" s="3">
+        <v>-20.8565380652127</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.316806252818843</v>
+      </c>
+      <c r="F4" s="5">
+        <v>-0.10330216627232899</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1.82164174970153E-3</v>
       </c>
       <c r="H4">
-        <v>490</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1149,25 +1167,25 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>-2.4152365583794002E-9</v>
+        <v>-2.3384657677458001E-9</v>
       </c>
       <c r="C5">
-        <v>1.21062131176298E-10</v>
-      </c>
-      <c r="D5">
-        <v>-19.330061716906201</v>
-      </c>
-      <c r="E5">
-        <v>0.24111407783511701</v>
-      </c>
-      <c r="F5">
-        <v>-9.4474669051568302E-2</v>
-      </c>
-      <c r="G5">
-        <v>1.3442280671903399E-3</v>
+        <v>1.1715757461732101E-10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-19.233193480415501</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.23451904673235899</v>
+      </c>
+      <c r="F5" s="5">
+        <v>-9.3935074511343697E-2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1.30620720122671E-3</v>
       </c>
       <c r="H5">
-        <v>585</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/Copper/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Copper/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -42,34 +42,34 @@
     <t xml:space="preserve">n</t>
   </si>
   <si>
+    <t xml:space="preserve">Developed Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
   </si>
 </sst>
 </file>
@@ -435,25 +435,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00000000947704566571921</v>
+        <v>-0.00000000503683330322641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00000000127151484262287</v>
+        <v>0.000000000408370187200143</v>
       </c>
       <c r="E2" t="n">
-        <v>-34.0415137070108</v>
+        <v>-27.9812700410149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63753378383942</v>
+        <v>0.375851229143029</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.181319790559114</v>
+        <v>-0.143261194041551</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0042125159913637</v>
+        <v>0.0022460670238699</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -464,25 +464,25 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.00000000465431468033931</v>
+        <v>-0.00000000278013610282006</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00000000060862328090242</v>
+        <v>0.000000000226277213550921</v>
       </c>
       <c r="E3" t="n">
-        <v>-25.4521470015911</v>
+        <v>-21.8589834922976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.356183240066405</v>
+        <v>0.235295450575286</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.127707657684606</v>
+        <v>-0.107356008907272</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00206508377961345</v>
+        <v>0.00129484582590559</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
@@ -493,25 +493,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00000000276361213537488</v>
+        <v>-0.00000000176371484338359</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000000000357602376992745</v>
+        <v>0.00000000014312306896318</v>
       </c>
       <c r="E4" t="n">
-        <v>-20.3048994822695</v>
+        <v>-17.9320501077412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.227943093379676</v>
+        <v>0.161508265217867</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0986195291347268</v>
+        <v>-0.0859270205349749</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00123567958763713</v>
+        <v>0.000847450307983877</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -522,25 +522,25 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.00000000182978674555143</v>
+        <v>-0.00000000121884469964291</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000000000235413983534295</v>
+        <v>0.0000000000983830990732715</v>
       </c>
       <c r="E5" t="n">
-        <v>-16.884534216154</v>
+        <v>-15.2011714118437</v>
       </c>
       <c r="F5" t="n">
-        <v>0.158596116315182</v>
+        <v>0.117895897904221</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0803409450400213</v>
+        <v>-0.0716604576127089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000824921725281657</v>
+        <v>0.000599564255970692</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -551,25 +551,25 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00000000130062106621956</v>
+        <v>-0.000000000892799889656021</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000000000166725095481048</v>
+        <v>0.0000000000716627936083053</v>
       </c>
       <c r="E6" t="n">
-        <v>-14.4487676230536</v>
+        <v>-13.1924923491801</v>
       </c>
       <c r="F6" t="n">
-        <v>0.116852731776691</v>
+        <v>0.0899284739120021</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0677854184174354</v>
+        <v>-0.0614706914602118</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000590934696985035</v>
+        <v>0.000447291087215683</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -580,25 +580,25 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.00000000928658394719157</v>
+        <v>-0.0000000119059117242522</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00000000260319570597097</v>
+        <v>0.00000000225982707275541</v>
       </c>
       <c r="E7" t="n">
-        <v>-31.2537812490728</v>
+        <v>-24.4817675872995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.525408251121681</v>
+        <v>0.535210798302274</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.16389943093616</v>
+        <v>-0.12324963046968</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00328010201992025</v>
+        <v>0.00295674691007959</v>
       </c>
       <c r="I7" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8">
@@ -609,25 +609,25 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.00000000476738248263856</v>
+        <v>-0.00000000693655114392823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00000000145833273144917</v>
+        <v>0.00000000127972129276601</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.807263537815</v>
+        <v>-19.6532754118314</v>
       </c>
       <c r="F8" t="n">
-        <v>0.317185090512003</v>
+        <v>0.382505466733765</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.118428021695456</v>
+        <v>-0.0956247370544886</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00178998574456589</v>
+        <v>0.00199986079517363</v>
       </c>
       <c r="I8" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
@@ -638,25 +638,25 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.00000000286821669007063</v>
+        <v>-0.00000000447208239469706</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00000000090694230920385</v>
+        <v>0.000000000792823171805017</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.2233018334837</v>
+        <v>-16.394265508948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.213209476790484</v>
+        <v>0.288801513753192</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0928516804973768</v>
+        <v>-0.0780785227230666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00113767832353614</v>
+        <v>0.00145933818440488</v>
       </c>
       <c r="I9" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -667,25 +667,25 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.00000000189971648855015</v>
+        <v>-0.0000000031052782575033</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000000000605120152615383</v>
+        <v>0.000000000530174947968209</v>
       </c>
       <c r="E10" t="n">
-        <v>-16.1194762503991</v>
+        <v>-14.0566600272471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.153598408676707</v>
+        <v>0.226644723961649</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0764053468973041</v>
+        <v>-0.0659721800435055</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000790761633399643</v>
+        <v>0.00111883018249847</v>
       </c>
       <c r="I10" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -696,25 +696,25 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.00000000134443626084822</v>
+        <v>-0.0000000022776386031791</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000000000426784104791067</v>
+        <v>0.000000000376311755049718</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.8788674552928</v>
+        <v>-12.3015203532517</v>
       </c>
       <c r="F11" t="n">
-        <v>0.116078615071631</v>
+        <v>0.183159399805892</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0649263513353495</v>
+        <v>-0.0571241054832038</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000582836525683773</v>
+        <v>0.000888954991499451</v>
       </c>
       <c r="I11" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -725,25 +725,25 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.00000000503683330322641</v>
+        <v>-0.00000000431212662469429</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000000000408370187200143</v>
+        <v>0.000000000732510674399534</v>
       </c>
       <c r="E12" t="n">
-        <v>-27.9812700410149</v>
+        <v>-39.2443546078952</v>
       </c>
       <c r="F12" t="n">
-        <v>0.375851229143029</v>
+        <v>0.908466087854785</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.143261194041551</v>
+        <v>-0.217024126734495</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0022460670238699</v>
+        <v>0.00633693598334707</v>
       </c>
       <c r="I12" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -754,25 +754,25 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.00000000278013610282006</v>
+        <v>-0.00000000184125693789807</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000000000226277213550921</v>
+        <v>0.000000000298774498861813</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.8589834922976</v>
+        <v>-28.1862503999904</v>
       </c>
       <c r="F13" t="n">
-        <v>0.235295450575286</v>
+        <v>0.481881337044835</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.107356008907272</v>
+        <v>-0.143917388131278</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00129484582590559</v>
+        <v>0.00287786577037895</v>
       </c>
       <c r="I13" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00000000176371484338359</v>
+        <v>-0.00000000102224736035393</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00000000014312306896318</v>
+        <v>0.000000000162168698509139</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.9320501077412</v>
+        <v>-21.9860667878466</v>
       </c>
       <c r="F14" t="n">
-        <v>0.161508265217867</v>
+        <v>0.29777385282192</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0859270205349749</v>
+        <v>-0.107868538314292</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000847450307983877</v>
+        <v>0.00164514860302336</v>
       </c>
       <c r="I14" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -812,25 +812,25 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.00000000121884469964291</v>
+        <v>-0.000000000650526269084162</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0000000000983830990732715</v>
+        <v>0.000000000101814451582528</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.2011714118437</v>
+        <v>-18.0216151340535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.117895897904221</v>
+        <v>0.202070243403988</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0716604576127089</v>
+        <v>-0.0863176783693471</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000599564255970692</v>
+        <v>0.00106509249819166</v>
       </c>
       <c r="I15" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -841,25 +841,25 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.000000000892799889656021</v>
+        <v>-0.000000000450472994053227</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0000000000716627936083053</v>
+        <v>0.0000000000698706871238354</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.1924923491801</v>
+        <v>-15.2693905045291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0899284739120021</v>
+        <v>0.146161932400706</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0614706914602118</v>
+        <v>-0.0719680291788789</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000447291087215683</v>
+        <v>0.000746457703950461</v>
       </c>
       <c r="I16" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -870,25 +870,25 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.00000000431212662469429</v>
+        <v>-0.00000000928658394719157</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000000000732510674399534</v>
+        <v>0.00000000260319570597097</v>
       </c>
       <c r="E17" t="n">
-        <v>-39.2443546078952</v>
+        <v>-31.2537812490728</v>
       </c>
       <c r="F17" t="n">
-        <v>0.908466087854785</v>
+        <v>0.525408251121681</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.217024126734495</v>
+        <v>-0.16389943093616</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00633693598334707</v>
+        <v>0.00328010201992025</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -899,25 +899,25 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00000000184125693789807</v>
+        <v>-0.00000000476738248263856</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000000000298774498861813</v>
+        <v>0.00000000145833273144917</v>
       </c>
       <c r="E18" t="n">
-        <v>-28.1862503999904</v>
+        <v>-23.807263537815</v>
       </c>
       <c r="F18" t="n">
-        <v>0.481881337044835</v>
+        <v>0.317185090512003</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.143917388131278</v>
+        <v>-0.118428021695456</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00287786577037895</v>
+        <v>0.00178998574456589</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -928,25 +928,25 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.00000000102224736035393</v>
+        <v>-0.00000000286821669007063</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000000000162168698509139</v>
+        <v>0.00000000090694230920385</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.9860667878466</v>
+        <v>-19.2233018334837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.29777385282192</v>
+        <v>0.213209476790484</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.107868538314292</v>
+        <v>-0.0928516804973768</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00164514860302336</v>
+        <v>0.00113767832353614</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.000000000650526269084162</v>
+        <v>-0.00000000189971648855015</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000000000101814451582528</v>
+        <v>0.000000000605120152615383</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.0216151340535</v>
+        <v>-16.1194762503991</v>
       </c>
       <c r="F20" t="n">
-        <v>0.202070243403988</v>
+        <v>0.153598408676707</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0863176783693471</v>
+        <v>-0.0764053468973041</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00106509249819166</v>
+        <v>0.000790761633399643</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -986,25 +986,25 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.000000000450472994053227</v>
+        <v>-0.00000000134443626084822</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0000000000698706871238354</v>
+        <v>0.000000000426784104791067</v>
       </c>
       <c r="E21" t="n">
-        <v>-15.2693905045291</v>
+        <v>-13.8788674552928</v>
       </c>
       <c r="F21" t="n">
-        <v>0.146161932400706</v>
+        <v>0.116078615071631</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0719680291788789</v>
+        <v>-0.0649263513353495</v>
       </c>
       <c r="H21" t="n">
-        <v>0.000746457703950461</v>
+        <v>0.000582836525683773</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0000000119059117242522</v>
+        <v>-0.00000000947704566571921</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00000000225982707275541</v>
+        <v>0.00000000127151484262287</v>
       </c>
       <c r="E22" t="n">
-        <v>-24.4817675872995</v>
+        <v>-34.0415137070108</v>
       </c>
       <c r="F22" t="n">
-        <v>0.535210798302274</v>
+        <v>0.63753378383942</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.12324963046968</v>
+        <v>-0.181319790559114</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00295674691007959</v>
+        <v>0.0042125159913637</v>
       </c>
       <c r="I22" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1044,25 +1044,25 @@
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.00000000693655114392823</v>
+        <v>-0.00000000465431468033931</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00000000127972129276601</v>
+        <v>0.00000000060862328090242</v>
       </c>
       <c r="E23" t="n">
-        <v>-19.6532754118314</v>
+        <v>-25.4521470015911</v>
       </c>
       <c r="F23" t="n">
-        <v>0.382505466733765</v>
+        <v>0.356183240066405</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0956247370544886</v>
+        <v>-0.127707657684606</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00199986079517363</v>
+        <v>0.00206508377961345</v>
       </c>
       <c r="I23" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1073,25 +1073,25 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00000000447208239469706</v>
+        <v>-0.00000000276361213537488</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000000000792823171805017</v>
+        <v>0.000000000357602376992745</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.394265508948</v>
+        <v>-20.3048994822695</v>
       </c>
       <c r="F24" t="n">
-        <v>0.288801513753192</v>
+        <v>0.227943093379676</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0780785227230666</v>
+        <v>-0.0986195291347268</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00145933818440488</v>
+        <v>0.00123567958763713</v>
       </c>
       <c r="I24" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1102,25 +1102,25 @@
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0000000031052782575033</v>
+        <v>-0.00000000182978674555143</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000000000530174947968209</v>
+        <v>0.000000000235413983534295</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.0566600272471</v>
+        <v>-16.884534216154</v>
       </c>
       <c r="F25" t="n">
-        <v>0.226644723961649</v>
+        <v>0.158596116315182</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0659721800435055</v>
+        <v>-0.0803409450400213</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00111883018249847</v>
+        <v>0.000824921725281657</v>
       </c>
       <c r="I25" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1131,25 +1131,25 @@
         <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0000000022776386031791</v>
+        <v>-0.00000000130062106621956</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000000000376311755049718</v>
+        <v>0.000000000166725095481048</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.3015203532517</v>
+        <v>-14.4487676230536</v>
       </c>
       <c r="F26" t="n">
-        <v>0.183159399805892</v>
+        <v>0.116852731776691</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0571241054832038</v>
+        <v>-0.0677854184174354</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000888954991499451</v>
+        <v>0.000590934696985035</v>
       </c>
       <c r="I26" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1194,25 +1194,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00000000400507605864088</v>
+        <v>-0.0000000023384657677458</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000000000380217085845979</v>
+        <v>0.000000000117157574617321</v>
       </c>
       <c r="D2" t="n">
-        <v>-22.2263724060158</v>
+        <v>-19.2331934804155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.591687348517964</v>
+        <v>0.234519046732359</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.111154668167181</v>
+        <v>-0.0939350745113437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00345577630146671</v>
+        <v>0.00130620720122671</v>
       </c>
       <c r="H2" t="n">
-        <v>150</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
@@ -1220,25 +1220,25 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.00000000403326717385982</v>
+        <v>-0.00000000573949242471197</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000652086785597082</v>
+        <v>0.000000000573399428609561</v>
       </c>
       <c r="D3" t="n">
-        <v>-20.8565380652127</v>
+        <v>-17.3774977777155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.316806252818843</v>
+        <v>0.230994605405206</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.103302166272329</v>
+        <v>-0.0840098351547888</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00182164174970153</v>
+        <v>0.00124190077293871</v>
       </c>
       <c r="H3" t="n">
-        <v>465</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4">
@@ -1246,25 +1246,25 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0000000023384657677458</v>
+        <v>-0.00000000165532603721674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000000000117157574617321</v>
+        <v>0.000000000232386765519311</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.2331934804155</v>
+        <v>-24.541535486863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.234519046732359</v>
+        <v>1.04974572349161</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0939350745113437</v>
+        <v>-0.125419152145658</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00130620720122671</v>
+        <v>0.00639621921866563</v>
       </c>
       <c r="H4" t="n">
-        <v>610</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -1272,25 +1272,25 @@
         <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00000000165532603721674</v>
+        <v>-0.00000000403326717385982</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000000000232386765519311</v>
+        <v>0.000000000652086785597082</v>
       </c>
       <c r="D5" t="n">
-        <v>-24.541535486863</v>
+        <v>-20.8565380652127</v>
       </c>
       <c r="E5" t="n">
-        <v>1.04974572349161</v>
+        <v>0.316806252818843</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.125419152145658</v>
+        <v>-0.103302166272329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00639621921866563</v>
+        <v>0.00182164174970153</v>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6">
@@ -1298,25 +1298,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.00000000573949242471197</v>
+        <v>-0.00000000400507605864088</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000000000573399428609561</v>
+        <v>0.000000000380217085845979</v>
       </c>
       <c r="D6" t="n">
-        <v>-17.3774977777155</v>
+        <v>-22.2263724060158</v>
       </c>
       <c r="E6" t="n">
-        <v>0.230994605405206</v>
+        <v>0.591687348517964</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0840098351547888</v>
+        <v>-0.111154668167181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00124190077293871</v>
+        <v>0.00345577630146671</v>
       </c>
       <c r="H6" t="n">
-        <v>635</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
